--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/IOWA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/IOWA_2012.xlsx
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C124">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C442">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C482">
